--- a/data/output/sim_gridrnd/ABS1/group_480_60/results/ABS1_G3_results_summary.xlsx
+++ b/data/output/sim_gridrnd/ABS1/group_480_60/results/ABS1_G3_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,876 +466,997 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G3_481_59_ABS1</t>
+          <t>S01_G3_478_60_ABS1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C2" t="n">
-        <v>59</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D2" t="n">
-        <v>87.47220163083766</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>73.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>452.483559076916</v>
-      </c>
-      <c r="J2" t="n">
-        <v>86.75701118652749</v>
-      </c>
-      <c r="K2" t="n">
-        <v>461.3715181785399</v>
-      </c>
-      <c r="L2" t="n">
-        <v>82.09691362064025</v>
-      </c>
-      <c r="M2" t="n">
-        <v>457.8006278942939</v>
-      </c>
-      <c r="N2" t="n">
-        <v>84.67396764438742</v>
-      </c>
-      <c r="O2" t="n">
-        <v>461.7659543982111</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77.82395095170065</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>464.6034149635639</v>
-      </c>
       <c r="R2" t="n">
-        <v>73.7463992382031</v>
+        <v>501.66</v>
       </c>
       <c r="S2" t="n">
-        <v>458.3625447250994</v>
+        <v>35.84</v>
       </c>
       <c r="T2" t="n">
-        <v>74.2198552072884</v>
+        <v>505.07</v>
       </c>
       <c r="U2" t="n">
-        <v>463.0598464969968</v>
+        <v>39.62</v>
       </c>
       <c r="V2" t="n">
-        <v>68.95930082739942</v>
+        <v>503.24</v>
       </c>
       <c r="W2" t="n">
-        <v>464.0083320779111</v>
+        <v>40.62</v>
       </c>
       <c r="X2" t="n">
-        <v>67.44428458367729</v>
+        <v>498.51</v>
       </c>
       <c r="Y2" t="n">
-        <v>466.4568179186926</v>
+        <v>38.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>64.57197213124849</v>
+        <v>497.35</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.55</v>
+        <v>40.68</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.3333333333333333</v>
+        <v>494.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.25</v>
+        <v>51.01</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.2</v>
+        <v>499.55</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.1666666666666667</v>
+        <v>52.37</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1571428571428571</v>
+        <v>500.39</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.1375</v>
+        <v>47.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.1333333333333333</v>
+        <v>496.21</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.13</v>
+        <v>57.38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>451.975</v>
+        <v>0.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>455.45</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="AL2" t="n">
-        <v>457.55</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>458.28</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>459</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="AO2" t="n">
-        <v>458.5357142857143</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="AP2" t="n">
-        <v>459.21875</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>459.1111111111111</v>
+        <v>0.01111111111111111</v>
       </c>
       <c r="AR2" t="n">
-        <v>459.28</v>
+        <v>-0.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>55.79224296441217</v>
+        <v>501.275</v>
       </c>
       <c r="AT2" t="n">
-        <v>66.81851664521345</v>
+        <v>501.7333333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>71.67686167795016</v>
+        <v>501.1625</v>
       </c>
       <c r="AV2" t="n">
-        <v>74.30559602075741</v>
+        <v>500.64</v>
       </c>
       <c r="AW2" t="n">
-        <v>74.91995728776145</v>
+        <v>500.475</v>
       </c>
       <c r="AX2" t="n">
-        <v>74.41816317408058</v>
+        <v>497.3714285714286</v>
       </c>
       <c r="AY2" t="n">
-        <v>73.71437036587574</v>
+        <v>498.125</v>
       </c>
       <c r="AZ2" t="n">
-        <v>72.15961388854024</v>
+        <v>499.0444444444444</v>
       </c>
       <c r="BA2" t="n">
-        <v>70.37585949741573</v>
+        <v>496.365</v>
       </c>
       <c r="BB2" t="n">
-        <v>360</v>
+        <v>47.95153151881595</v>
       </c>
       <c r="BC2" t="n">
-        <v>356</v>
+        <v>47.48398560450553</v>
       </c>
       <c r="BD2" t="n">
-        <v>356</v>
+        <v>46.20293382189057</v>
       </c>
       <c r="BE2" t="n">
-        <v>356</v>
+        <v>44.98811398580741</v>
       </c>
       <c r="BF2" t="n">
-        <v>356</v>
+        <v>43.42809430541478</v>
       </c>
       <c r="BG2" t="n">
-        <v>356</v>
+        <v>45.03194784295492</v>
       </c>
       <c r="BH2" t="n">
-        <v>356</v>
+        <v>46.74087477786439</v>
       </c>
       <c r="BI2" t="n">
-        <v>356</v>
+        <v>47.6285187935667</v>
       </c>
       <c r="BJ2" t="n">
-        <v>356</v>
+        <v>49.23750374460509</v>
       </c>
       <c r="BK2" t="n">
-        <v>542</v>
+        <v>372</v>
       </c>
       <c r="BL2" t="n">
-        <v>555</v>
+        <v>372</v>
       </c>
       <c r="BM2" t="n">
-        <v>557</v>
+        <v>372</v>
       </c>
       <c r="BN2" t="n">
-        <v>557</v>
+        <v>372</v>
       </c>
       <c r="BO2" t="n">
-        <v>557</v>
+        <v>372</v>
       </c>
       <c r="BP2" t="n">
-        <v>557</v>
+        <v>372</v>
       </c>
       <c r="BQ2" t="n">
-        <v>557</v>
+        <v>372</v>
       </c>
       <c r="BR2" t="n">
-        <v>557</v>
+        <v>372</v>
       </c>
       <c r="BS2" t="n">
-        <v>557</v>
+        <v>372</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.5</v>
+        <v>602</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.7142857142857143</v>
+        <v>602</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.625</v>
+        <v>602</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.3846153846153846</v>
+        <v>602</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.2777777777777778</v>
+        <v>602</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.25</v>
+        <v>602</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.84</v>
+        <v>602</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.7241379310344828</v>
+        <v>602</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.7</v>
+        <v>602</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.9655172413793104</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>496.21</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>57.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S03_G3_478_61_ABS1</t>
+          <t>S02_G3_481_59_ABS1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D3" t="n">
-        <v>90.43736100815418</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>461.1411333443776</v>
-      </c>
-      <c r="J3" t="n">
-        <v>50.93408746492084</v>
-      </c>
-      <c r="K3" t="n">
-        <v>459.991907079547</v>
-      </c>
-      <c r="L3" t="n">
-        <v>68.3927662262134</v>
-      </c>
-      <c r="M3" t="n">
-        <v>456.9566257490918</v>
-      </c>
-      <c r="N3" t="n">
-        <v>62.5618058303241</v>
-      </c>
-      <c r="O3" t="n">
-        <v>464.057197269439</v>
-      </c>
-      <c r="P3" t="n">
-        <v>58.11057030940571</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>467.5136705241462</v>
-      </c>
       <c r="R3" t="n">
-        <v>65.93790371812089</v>
+        <v>452.48</v>
       </c>
       <c r="S3" t="n">
-        <v>467.3708855526915</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>72.81581866007978</v>
+        <v>461.37</v>
       </c>
       <c r="U3" t="n">
-        <v>470.2557117706529</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>73.96544906319065</v>
+        <v>457.8</v>
       </c>
       <c r="W3" t="n">
-        <v>465.7002736173417</v>
+        <v>84.67</v>
       </c>
       <c r="X3" t="n">
-        <v>75.72827560801562</v>
+        <v>461.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>462.944881648226</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>75.80290667822608</v>
+        <v>464.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.35</v>
+        <v>73.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.2666666666666667</v>
+        <v>458.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.225</v>
+        <v>74.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.16</v>
+        <v>463.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.1</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.08571428571428572</v>
+        <v>464.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.05</v>
+        <v>67.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.05555555555555555</v>
+        <v>466.46</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.06</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>473.725</v>
+        <v>-0.55</v>
       </c>
       <c r="AK3" t="n">
-        <v>465</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AL3" t="n">
-        <v>460.8</v>
+        <v>-0.25</v>
       </c>
       <c r="AM3" t="n">
-        <v>461.42</v>
+        <v>-0.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>464.8333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="AO3" t="n">
-        <v>465.0357142857143</v>
+        <v>-0.1571428571428571</v>
       </c>
       <c r="AP3" t="n">
-        <v>467.90625</v>
+        <v>-0.1375</v>
       </c>
       <c r="AQ3" t="n">
-        <v>467.3055555555555</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="AR3" t="n">
-        <v>466.125</v>
+        <v>-0.13</v>
       </c>
       <c r="AS3" t="n">
-        <v>53.9351404466513</v>
+        <v>451.975</v>
       </c>
       <c r="AT3" t="n">
-        <v>59.14332873057901</v>
+        <v>455.45</v>
       </c>
       <c r="AU3" t="n">
-        <v>62.48147725526342</v>
+        <v>457.55</v>
       </c>
       <c r="AV3" t="n">
-        <v>62.42149950137372</v>
+        <v>458.28</v>
       </c>
       <c r="AW3" t="n">
-        <v>64.46450358315204</v>
+        <v>459</v>
       </c>
       <c r="AX3" t="n">
-        <v>66.54412185205561</v>
+        <v>458.5357142857143</v>
       </c>
       <c r="AY3" t="n">
-        <v>69.35495628242801</v>
+        <v>459.21875</v>
       </c>
       <c r="AZ3" t="n">
-        <v>70.00143627274311</v>
+        <v>459.1111111111111</v>
       </c>
       <c r="BA3" t="n">
-        <v>70.57031511195058</v>
+        <v>459.28</v>
       </c>
       <c r="BB3" t="n">
-        <v>397</v>
+        <v>55.79224296441217</v>
       </c>
       <c r="BC3" t="n">
-        <v>372</v>
+        <v>66.81851664521345</v>
       </c>
       <c r="BD3" t="n">
-        <v>370</v>
+        <v>71.67686167795016</v>
       </c>
       <c r="BE3" t="n">
-        <v>370</v>
+        <v>74.30559602075741</v>
       </c>
       <c r="BF3" t="n">
-        <v>370</v>
+        <v>74.91995728776145</v>
       </c>
       <c r="BG3" t="n">
-        <v>370</v>
+        <v>74.41816317408058</v>
       </c>
       <c r="BH3" t="n">
-        <v>370</v>
+        <v>73.71437036587574</v>
       </c>
       <c r="BI3" t="n">
-        <v>370</v>
+        <v>72.15961388854024</v>
       </c>
       <c r="BJ3" t="n">
-        <v>370</v>
+        <v>70.37585949741573</v>
       </c>
       <c r="BK3" t="n">
-        <v>632</v>
+        <v>360</v>
       </c>
       <c r="BL3" t="n">
-        <v>632</v>
+        <v>356</v>
       </c>
       <c r="BM3" t="n">
-        <v>632</v>
+        <v>356</v>
       </c>
       <c r="BN3" t="n">
-        <v>632</v>
+        <v>356</v>
       </c>
       <c r="BO3" t="n">
-        <v>632</v>
+        <v>356</v>
       </c>
       <c r="BP3" t="n">
-        <v>632</v>
+        <v>356</v>
       </c>
       <c r="BQ3" t="n">
-        <v>632</v>
+        <v>356</v>
       </c>
       <c r="BR3" t="n">
-        <v>632</v>
+        <v>356</v>
       </c>
       <c r="BS3" t="n">
-        <v>632</v>
+        <v>356</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>542</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.8</v>
+        <v>555</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9166666666666666</v>
+        <v>557</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8823529411764706</v>
+        <v>557</v>
       </c>
       <c r="BX3" t="n">
-        <v>1</v>
+        <v>557</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.9090909090909091</v>
+        <v>557</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.8695652173913043</v>
+        <v>557</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.8571428571428571</v>
+        <v>557</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.7878787878787878</v>
+        <v>557</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>466.46</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>64.56999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S01_G3_478_60_ABS1</t>
+          <t>S03_G3_478_61_ABS1</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>478</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D4" t="n">
-        <v>88.95478131949592</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
         <v>478</v>
@@ -1344,228 +1465,261 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>74</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>501.6551283042388</v>
-      </c>
-      <c r="J4" t="n">
-        <v>35.84394843786424</v>
-      </c>
-      <c r="K4" t="n">
-        <v>505.0665083972871</v>
-      </c>
-      <c r="L4" t="n">
-        <v>39.62041617700744</v>
-      </c>
-      <c r="M4" t="n">
-        <v>503.2414034154373</v>
-      </c>
-      <c r="N4" t="n">
-        <v>40.61732418154645</v>
-      </c>
-      <c r="O4" t="n">
-        <v>498.5063395107337</v>
-      </c>
-      <c r="P4" t="n">
-        <v>38.3974854218692</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>497.3486201743609</v>
-      </c>
       <c r="R4" t="n">
-        <v>40.67604963160282</v>
+        <v>461.14</v>
       </c>
       <c r="S4" t="n">
-        <v>494.1711666276433</v>
+        <v>50.93</v>
       </c>
       <c r="T4" t="n">
-        <v>51.01212585235517</v>
+        <v>459.99</v>
       </c>
       <c r="U4" t="n">
-        <v>499.5464147847634</v>
+        <v>68.39</v>
       </c>
       <c r="V4" t="n">
-        <v>52.3670655877339</v>
+        <v>456.96</v>
       </c>
       <c r="W4" t="n">
-        <v>500.3868644058369</v>
+        <v>62.56</v>
       </c>
       <c r="X4" t="n">
-        <v>47.49957946287187</v>
+        <v>464.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>496.2051057836092</v>
+        <v>58.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>57.3843684338534</v>
+        <v>467.51</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05</v>
+        <v>65.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03333333333333333</v>
+        <v>467.37</v>
       </c>
       <c r="AC4" t="n">
+        <v>72.81999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>470.26</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>73.97</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>465.7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>75.73</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>462.94</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.225</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.08571428571428572</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.05555555555555555</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>473.725</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>465</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>461.42</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>464.8333333333333</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>465.0357142857143</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>467.90625</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>467.3055555555555</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>466.125</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>53.9351404466513</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>59.14332873057901</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>62.48147725526342</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>62.42149950137372</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>64.46450358315204</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>66.54412185205561</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>69.35495628242801</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>70.00143627274311</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>70.57031511195058</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>397</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>372</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>370</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>370</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>370</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>370</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>370</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>370</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>370</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>632</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>632</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>632</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>632</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>632</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>632</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>632</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>632</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>632</v>
+      </c>
+      <c r="CC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.01666666666666667</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-0.02857142857142857</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.01111111111111111</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>501.275</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>501.7333333333333</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>501.1625</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500.64</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>500.475</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>497.3714285714286</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>498.125</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>499.0444444444444</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>496.365</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>47.95153151881595</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>47.48398560450553</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>46.20293382189057</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>44.98811398580741</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>43.42809430541478</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>45.03194784295492</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>46.74087477786439</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>47.6285187935667</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>49.23750374460509</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>372</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>372</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>372</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>372</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>372</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>372</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>372</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>372</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>372</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>602</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>602</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>602</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>602</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>602</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>602</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>602</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>602</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>602</v>
-      </c>
-      <c r="BT4" t="n">
+      <c r="CD4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CG4" t="n">
         <v>1</v>
       </c>
-      <c r="BU4" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0.6818181818181818</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.7037037037037037</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.9655172413793104</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>0</v>
+      <c r="CH4" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>462.94</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>75.8</v>
       </c>
     </row>
     <row r="5">
@@ -1578,10 +1732,10 @@
         <v>479</v>
       </c>
       <c r="C5" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D5" t="n">
         <v>58</v>
-      </c>
-      <c r="D5" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E5" t="n">
         <v>479</v>
@@ -1590,228 +1744,261 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>514.6061019966428</v>
-      </c>
-      <c r="J5" t="n">
-        <v>109.6990843414186</v>
-      </c>
-      <c r="K5" t="n">
-        <v>505.2897750115247</v>
-      </c>
-      <c r="L5" t="n">
-        <v>112.7931966634515</v>
-      </c>
-      <c r="M5" t="n">
-        <v>499.5918327744949</v>
-      </c>
-      <c r="N5" t="n">
-        <v>94.87454182396189</v>
-      </c>
-      <c r="O5" t="n">
-        <v>493.2418936437755</v>
-      </c>
-      <c r="P5" t="n">
-        <v>92.07295216418424</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>491.7076064499992</v>
-      </c>
       <c r="R5" t="n">
-        <v>86.68520972823302</v>
+        <v>514.61</v>
       </c>
       <c r="S5" t="n">
-        <v>486.4665631031921</v>
+        <v>109.7</v>
       </c>
       <c r="T5" t="n">
-        <v>85.12780106624686</v>
+        <v>505.29</v>
       </c>
       <c r="U5" t="n">
-        <v>485.2789580383712</v>
+        <v>112.79</v>
       </c>
       <c r="V5" t="n">
-        <v>83.23470406907714</v>
+        <v>499.59</v>
       </c>
       <c r="W5" t="n">
-        <v>482.1498206476605</v>
+        <v>94.87</v>
       </c>
       <c r="X5" t="n">
-        <v>77.43895425949073</v>
+        <v>493.24</v>
       </c>
       <c r="Y5" t="n">
-        <v>479.2726585077368</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>81.80767911568611</v>
+        <v>491.71</v>
       </c>
       <c r="AA5" t="n">
+        <v>86.69</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>486.47</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>85.13</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>485.28</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>83.23</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>482.15</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>77.44</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>479.27</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AK5" t="n">
         <v>-0.01694915254237288</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AL5" t="n">
         <v>-0.01265822784810127</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AM5" t="n">
         <v>-0.0303030303030303</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AN5" t="n">
         <v>-0.04201680672268908</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AO5" t="n">
         <v>-0.03597122302158273</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AP5" t="n">
         <v>-0.01886792452830189</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AQ5" t="n">
         <v>0.01675977653631285</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AR5" t="n">
         <v>-0.02512562814070352</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AS5" t="n">
         <v>514.85</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
         <v>505.7666666666667</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AU5" t="n">
         <v>504.5</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AV5" t="n">
         <v>501.08</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AW5" t="n">
         <v>498.475</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
         <v>497.4571428571429</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AY5" t="n">
         <v>496.825</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AZ5" t="n">
         <v>497.3166666666667</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
         <v>492.31</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BB5" t="n">
         <v>66.57985806533385</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BC5" t="n">
         <v>71.14032299305055</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
         <v>75.49370834711989</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BE5" t="n">
         <v>78.70091231999791</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
         <v>80.61223671585681</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BG5" t="n">
         <v>81.8102658095959</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
         <v>81.37809517923112</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BI5" t="n">
         <v>79.9829478354258</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BJ5" t="n">
         <v>80.10239634368001</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
         <v>362</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BL5" t="n">
         <v>362</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BM5" t="n">
         <v>362</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BN5" t="n">
         <v>362</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BO5" t="n">
         <v>362</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BP5" t="n">
         <v>362</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BQ5" t="n">
         <v>362</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BR5" t="n">
         <v>362</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BS5" t="n">
         <v>362</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BT5" t="n">
         <v>644</v>
       </c>
-      <c r="BL5" t="n">
+      <c r="BU5" t="n">
         <v>644</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BV5" t="n">
         <v>644</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BW5" t="n">
         <v>644</v>
       </c>
-      <c r="BO5" t="n">
+      <c r="BX5" t="n">
         <v>644</v>
       </c>
-      <c r="BP5" t="n">
+      <c r="BY5" t="n">
         <v>644</v>
       </c>
-      <c r="BQ5" t="n">
+      <c r="BZ5" t="n">
         <v>644</v>
       </c>
-      <c r="BR5" t="n">
+      <c r="CA5" t="n">
         <v>644</v>
       </c>
-      <c r="BS5" t="n">
+      <c r="CB5" t="n">
         <v>644</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="CC5" t="n">
         <v>0.625</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CD5" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="CE5" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="CF5" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="CG5" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CH5" t="n">
         <v>1</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CI5" t="n">
         <v>0.896551724137931</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CJ5" t="n">
         <v>0.7878787878787878</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CK5" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>479.27</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>81.81</v>
       </c>
     </row>
     <row r="6">
@@ -1824,10 +2011,10 @@
         <v>478</v>
       </c>
       <c r="C6" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D6" t="n">
         <v>59</v>
-      </c>
-      <c r="D6" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E6" t="n">
         <v>478</v>
@@ -1836,228 +2023,261 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>505.3222081515157</v>
-      </c>
-      <c r="J6" t="n">
-        <v>18.27767879864867</v>
-      </c>
-      <c r="K6" t="n">
-        <v>501.5470811861418</v>
-      </c>
-      <c r="L6" t="n">
-        <v>31.07333090359579</v>
-      </c>
-      <c r="M6" t="n">
-        <v>493.320880474338</v>
-      </c>
-      <c r="N6" t="n">
-        <v>54.20849519499887</v>
-      </c>
-      <c r="O6" t="n">
-        <v>486.7466038886405</v>
-      </c>
-      <c r="P6" t="n">
-        <v>63.34760047908574</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>491.5371188504067</v>
-      </c>
       <c r="R6" t="n">
-        <v>69.40701852203777</v>
+        <v>505.32</v>
       </c>
       <c r="S6" t="n">
-        <v>492.7442882082008</v>
+        <v>18.28</v>
       </c>
       <c r="T6" t="n">
-        <v>69.42548991095948</v>
+        <v>501.55</v>
       </c>
       <c r="U6" t="n">
-        <v>494.5610599834969</v>
+        <v>31.07</v>
       </c>
       <c r="V6" t="n">
-        <v>66.35925875390181</v>
+        <v>493.32</v>
       </c>
       <c r="W6" t="n">
-        <v>493.1056082296129</v>
+        <v>54.21</v>
       </c>
       <c r="X6" t="n">
-        <v>62.87202625542946</v>
+        <v>486.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>489.5686282966642</v>
+        <v>63.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>63.80160227912597</v>
+        <v>491.54</v>
       </c>
       <c r="AA6" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>492.74</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>69.43000000000001</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>494.56</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>493.11</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>489.57</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>0.3</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AK6" t="n">
         <v>0.1</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AL6" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AM6" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AN6" t="n">
         <v>-0.08333333333333333</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AO6" t="n">
         <v>-0.04285714285714286</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AP6" t="n">
         <v>-0.0375</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AQ6" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AR6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AS6" t="n">
         <v>509.2</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AT6" t="n">
         <v>504.9333333333333</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AU6" t="n">
         <v>496.25</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AV6" t="n">
         <v>484.01</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AW6" t="n">
         <v>488.9166666666667</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AX6" t="n">
         <v>492.45</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AY6" t="n">
         <v>492.55</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AZ6" t="n">
         <v>492.8555555555556</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BA6" t="n">
         <v>492.28</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BB6" t="n">
         <v>29.19006680362345</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BC6" t="n">
         <v>32.02804326766709</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="BD6" t="n">
         <v>41.50948686746199</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="BE6" t="n">
         <v>54.68445757251324</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="BF6" t="n">
         <v>58.83643759515772</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="BG6" t="n">
         <v>63.98251156147503</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BH6" t="n">
         <v>65.36807324680757</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BI6" t="n">
         <v>65.19288664521461</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BJ6" t="n">
         <v>64.77300054806787</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BK6" t="n">
         <v>468</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BL6" t="n">
         <v>453</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BM6" t="n">
         <v>409</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BN6" t="n">
         <v>381</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BO6" t="n">
         <v>381</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BP6" t="n">
         <v>381</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BQ6" t="n">
         <v>381</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BR6" t="n">
         <v>381</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BS6" t="n">
         <v>381</v>
       </c>
-      <c r="BK6" t="n">
+      <c r="BT6" t="n">
         <v>623</v>
       </c>
-      <c r="BL6" t="n">
+      <c r="BU6" t="n">
         <v>623</v>
       </c>
-      <c r="BM6" t="n">
+      <c r="BV6" t="n">
         <v>623</v>
       </c>
-      <c r="BN6" t="n">
+      <c r="BW6" t="n">
         <v>623</v>
       </c>
-      <c r="BO6" t="n">
+      <c r="BX6" t="n">
         <v>623</v>
       </c>
-      <c r="BP6" t="n">
+      <c r="BY6" t="n">
         <v>623</v>
       </c>
-      <c r="BQ6" t="n">
+      <c r="BZ6" t="n">
         <v>623</v>
       </c>
-      <c r="BR6" t="n">
+      <c r="CA6" t="n">
         <v>623</v>
       </c>
-      <c r="BS6" t="n">
+      <c r="CB6" t="n">
         <v>623</v>
       </c>
-      <c r="BT6" t="n">
+      <c r="CC6" t="n">
         <v>0</v>
       </c>
-      <c r="BU6" t="n">
+      <c r="CD6" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BV6" t="n">
+      <c r="CE6" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW6" t="n">
+      <c r="CF6" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="CG6" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CH6" t="n">
         <v>0.8</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CI6" t="n">
         <v>0.8</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CJ6" t="n">
         <v>0.8095238095238095</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CK6" t="n">
         <v>0.9523809523809523</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>489.57</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>63.8</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>480</v>
       </c>
       <c r="C7" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D7" t="n">
         <v>59</v>
-      </c>
-      <c r="D7" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E7" t="n">
         <v>480</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>501.6011962179353</v>
-      </c>
-      <c r="J7" t="n">
-        <v>61.64657496430889</v>
-      </c>
-      <c r="K7" t="n">
-        <v>494.5912493760152</v>
-      </c>
-      <c r="L7" t="n">
-        <v>60.79941153524315</v>
-      </c>
-      <c r="M7" t="n">
-        <v>498.6579414356212</v>
-      </c>
-      <c r="N7" t="n">
-        <v>62.93737387550724</v>
-      </c>
-      <c r="O7" t="n">
-        <v>501.3508971761764</v>
-      </c>
-      <c r="P7" t="n">
-        <v>69.38874633039595</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>494.3293193874762</v>
-      </c>
       <c r="R7" t="n">
-        <v>73.65224025512991</v>
+        <v>501.6</v>
       </c>
       <c r="S7" t="n">
-        <v>494.0593214468546</v>
+        <v>61.65</v>
       </c>
       <c r="T7" t="n">
-        <v>67.99594613629766</v>
+        <v>494.59</v>
       </c>
       <c r="U7" t="n">
-        <v>492.4817350916821</v>
+        <v>60.8</v>
       </c>
       <c r="V7" t="n">
-        <v>88.00821003606468</v>
+        <v>498.66</v>
       </c>
       <c r="W7" t="n">
-        <v>494.3690138617731</v>
+        <v>62.94</v>
       </c>
       <c r="X7" t="n">
-        <v>92.77236500797983</v>
+        <v>501.35</v>
       </c>
       <c r="Y7" t="n">
-        <v>492.7640281634854</v>
+        <v>69.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>90.24411641794111</v>
+        <v>494.33</v>
       </c>
       <c r="AA7" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>494.06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>68</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>492.48</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>88.01000000000001</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>494.37</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>492.76</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AK7" t="n">
         <v>-0.06666666666666667</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AL7" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AM7" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AN7" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AO7" t="n">
         <v>-0.02857142857142857</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AP7" t="n">
         <v>-0.0375</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AQ7" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AR7" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AS7" t="n">
         <v>499.925</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>494.15</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>495.0875</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>498.18</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>497</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>496.3</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>494.75625</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>494.3944444444444</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>494.64</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>57.49060249292923</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>60.8344269308095</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>62.03027360692519</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>65.94154684263935</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>68.3158107614921</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>69.16343997063353</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>71.19759009922669</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>75.37016041011798</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>77.82878901794631</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>345</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>345</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>345</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>345</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>345</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>345</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>345</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>345</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>345</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BT7" t="n">
         <v>587</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BU7" t="n">
         <v>587</v>
       </c>
-      <c r="BM7" t="n">
+      <c r="BV7" t="n">
         <v>587</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BW7" t="n">
         <v>590</v>
       </c>
-      <c r="BO7" t="n">
+      <c r="BX7" t="n">
         <v>590</v>
       </c>
-      <c r="BP7" t="n">
+      <c r="BY7" t="n">
         <v>590</v>
       </c>
-      <c r="BQ7" t="n">
+      <c r="BZ7" t="n">
         <v>603</v>
       </c>
-      <c r="BR7" t="n">
+      <c r="CA7" t="n">
         <v>607</v>
       </c>
-      <c r="BS7" t="n">
+      <c r="CB7" t="n">
         <v>611</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="CC7" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>0.7</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.2307692307692308</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>0.6842105263157895</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.1904761904761905</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>0.9642857142857143</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>492.76</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>90.23999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>478</v>
       </c>
       <c r="C8" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D8" t="n">
         <v>58</v>
-      </c>
-      <c r="D8" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E8" t="n">
         <v>478</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>460.1737313092316</v>
-      </c>
-      <c r="J8" t="n">
-        <v>50.55467418004233</v>
-      </c>
-      <c r="K8" t="n">
-        <v>452.0498138595218</v>
-      </c>
-      <c r="L8" t="n">
-        <v>47.74050509050722</v>
-      </c>
-      <c r="M8" t="n">
-        <v>459.8369655319436</v>
-      </c>
-      <c r="N8" t="n">
-        <v>43.82610910225183</v>
-      </c>
-      <c r="O8" t="n">
-        <v>467.8016342775031</v>
-      </c>
-      <c r="P8" t="n">
-        <v>43.84159160432091</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>465.067483570968</v>
-      </c>
       <c r="R8" t="n">
-        <v>48.6518656045468</v>
+        <v>460.17</v>
       </c>
       <c r="S8" t="n">
-        <v>469.8102387377852</v>
+        <v>50.55</v>
       </c>
       <c r="T8" t="n">
-        <v>52.06657763878432</v>
+        <v>452.05</v>
       </c>
       <c r="U8" t="n">
-        <v>472.4646784246677</v>
+        <v>47.74</v>
       </c>
       <c r="V8" t="n">
-        <v>51.32778849883536</v>
+        <v>459.84</v>
       </c>
       <c r="W8" t="n">
-        <v>473.8368905340783</v>
+        <v>43.83</v>
       </c>
       <c r="X8" t="n">
-        <v>52.35152950153046</v>
+        <v>467.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>473.9689298454759</v>
+        <v>43.84</v>
       </c>
       <c r="Z8" t="n">
-        <v>57.50361345926147</v>
+        <v>465.07</v>
       </c>
       <c r="AA8" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>469.81</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>472.46</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>473.84</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>473.97</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
         <v>-0.3666666666666666</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AL8" t="n">
         <v>-0.3924050632911392</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AM8" t="n">
         <v>-0.3469387755102041</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AN8" t="n">
         <v>-0.2711864406779661</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AO8" t="n">
         <v>-0.1884057971014493</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AP8" t="n">
         <v>-0.1518987341772152</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AQ8" t="n">
         <v>-0.1348314606741573</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AR8" t="n">
         <v>-0.09090909090909091</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AS8" t="n">
         <v>461.075</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>457.25</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>456.0125</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>458.48</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>461.8666666666667</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>464.8714285714286</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>466.6375</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>467.4166666666667</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>470.075</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>62.20867604281576</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>57.6245390437095</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>54.57414537810006</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>52.29578950546592</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>52.07365510078542</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>52.32970241748027</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>52.38099458534555</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>52.48839818897548</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>53.33216079440247</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>377</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>377</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>377</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>377</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>377</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>377</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>377</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>377</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>377</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>639</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>639</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>639</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>639</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>639</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>639</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>639</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>639</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>639</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.2352941176470588</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.7586206896551724</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.8157894736842105</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.85</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>473.97</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>57.5</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>479</v>
       </c>
       <c r="C9" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D9" t="n">
         <v>61</v>
-      </c>
-      <c r="D9" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E9" t="n">
         <v>479</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>74</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>464.1461423277726</v>
-      </c>
-      <c r="J9" t="n">
-        <v>85.83055574685959</v>
-      </c>
-      <c r="K9" t="n">
-        <v>467.8900071044296</v>
-      </c>
-      <c r="L9" t="n">
-        <v>69.29552040379819</v>
-      </c>
-      <c r="M9" t="n">
-        <v>466.7182590182156</v>
-      </c>
-      <c r="N9" t="n">
-        <v>61.6740062392468</v>
-      </c>
-      <c r="O9" t="n">
-        <v>476.4655094191816</v>
-      </c>
-      <c r="P9" t="n">
-        <v>70.30417889674831</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>473.8493540304416</v>
-      </c>
       <c r="R9" t="n">
-        <v>66.32918789081441</v>
+        <v>464.15</v>
       </c>
       <c r="S9" t="n">
-        <v>481.0747697783881</v>
+        <v>85.83</v>
       </c>
       <c r="T9" t="n">
-        <v>70.79060082428146</v>
+        <v>467.89</v>
       </c>
       <c r="U9" t="n">
-        <v>480.7835980754394</v>
+        <v>69.3</v>
       </c>
       <c r="V9" t="n">
-        <v>66.8621404317693</v>
+        <v>466.72</v>
       </c>
       <c r="W9" t="n">
-        <v>483.639331369828</v>
+        <v>61.67</v>
       </c>
       <c r="X9" t="n">
-        <v>85.49303223707054</v>
+        <v>476.47</v>
       </c>
       <c r="Y9" t="n">
-        <v>482.5773698883322</v>
+        <v>70.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>83.54249962882797</v>
+        <v>473.85</v>
       </c>
       <c r="AA9" t="n">
+        <v>66.33</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>481.07</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>480.78</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>66.86</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>483.64</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>482.58</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AK9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AL9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AM9" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AN9" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AO9" t="n">
         <v>0</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AP9" t="n">
         <v>-0.025</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AQ9" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AR9" t="n">
         <v>0.02</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AS9" t="n">
         <v>464.175</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>467.55</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>466.825</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>470.05</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>470.975</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>473.8214285714286</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>473.11875</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>479.3277777777778</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>478.865</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>60.34521004189148</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>66.4355389331142</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>63.99194773563312</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>65.26107185757832</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>66.6842638233839</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>67.41007426375451</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>67.09437121277388</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>70.12471672001055</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>72.99764910598148</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>358</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>358</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>358</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>358</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>358</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>358</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>358</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>358</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>358</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>552</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>560</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BV9" t="n">
         <v>560</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BW9" t="n">
         <v>560</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BX9" t="n">
         <v>564</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BY9" t="n">
         <v>564</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BZ9" t="n">
         <v>564</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="CA9" t="n">
         <v>592</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="CB9" t="n">
         <v>594</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="CC9" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>1</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.9615384615384616</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>482.58</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>83.54000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>478</v>
       </c>
       <c r="C10" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D10" t="n">
         <v>60</v>
-      </c>
-      <c r="D10" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E10" t="n">
         <v>478</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>504.0879596985639</v>
-      </c>
-      <c r="J10" t="n">
-        <v>40.81194153815328</v>
-      </c>
-      <c r="K10" t="n">
-        <v>497.4909361737497</v>
-      </c>
-      <c r="L10" t="n">
-        <v>40.352807797808</v>
-      </c>
-      <c r="M10" t="n">
-        <v>494.1470161872001</v>
-      </c>
-      <c r="N10" t="n">
-        <v>61.41991935373476</v>
-      </c>
-      <c r="O10" t="n">
-        <v>480.6473284737277</v>
-      </c>
-      <c r="P10" t="n">
-        <v>91.92253060928641</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>476.6176093715246</v>
-      </c>
       <c r="R10" t="n">
-        <v>100.2363449658816</v>
+        <v>504.09</v>
       </c>
       <c r="S10" t="n">
-        <v>477.6220734786591</v>
+        <v>40.81</v>
       </c>
       <c r="T10" t="n">
-        <v>89.4548113650623</v>
+        <v>497.49</v>
       </c>
       <c r="U10" t="n">
-        <v>478.099313615757</v>
+        <v>40.35</v>
       </c>
       <c r="V10" t="n">
-        <v>81.60300246076194</v>
+        <v>494.15</v>
       </c>
       <c r="W10" t="n">
-        <v>479.8059824483092</v>
+        <v>61.42</v>
       </c>
       <c r="X10" t="n">
-        <v>78.33178582344078</v>
+        <v>480.65</v>
       </c>
       <c r="Y10" t="n">
-        <v>480.8666122192913</v>
+        <v>91.92</v>
       </c>
       <c r="Z10" t="n">
-        <v>79.65498577218736</v>
+        <v>476.62</v>
       </c>
       <c r="AA10" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>477.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>89.45</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>478.1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>479.81</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>480.87</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>79.65000000000001</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
         <v>-0.01694915254237288</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v>-0.0379746835443038</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v>-0.1717171717171717</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v>-0.2100840336134454</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v>-0.1942446043165468</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v>-0.169811320754717</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v>-0.1508379888268156</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v>-0.1256281407035176</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AS10" t="n">
         <v>515.725</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>508.0166666666667</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>502.1625</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>488.26</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>480.5916666666666</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>478.6357142857143</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>479.19375</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>478.9555555555556</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>479.865</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>53.06127943236952</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>48.77584500093828</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>51.873269549451</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>59.75025020868114</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>69.25526403979862</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>75.78128403639042</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>78.08044704621958</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>78.93371496404239</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>78.98947255805675</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>446</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>438</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>413</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>369</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>362</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>357</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>357</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>357</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>357</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>703</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>703</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>703</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>703</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>703</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>703</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>703</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>703</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>703</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.25</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.2</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>1</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>1</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.8235294117647058</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.9615384615384616</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>480.87</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>79.65000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>478</v>
       </c>
       <c r="C11" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D11" t="n">
         <v>59</v>
-      </c>
-      <c r="D11" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E11" t="n">
         <v>478</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>476.31694307256</v>
-      </c>
-      <c r="J11" t="n">
-        <v>39.33035539005406</v>
-      </c>
-      <c r="K11" t="n">
-        <v>482.668546718578</v>
-      </c>
-      <c r="L11" t="n">
-        <v>58.52755397854175</v>
-      </c>
-      <c r="M11" t="n">
-        <v>483.4424002456206</v>
-      </c>
-      <c r="N11" t="n">
-        <v>54.3718642404024</v>
-      </c>
-      <c r="O11" t="n">
-        <v>490.0084114903602</v>
-      </c>
-      <c r="P11" t="n">
-        <v>61.76226049455055</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>489.674286005082</v>
-      </c>
       <c r="R11" t="n">
-        <v>61.97523246494378</v>
+        <v>476.32</v>
       </c>
       <c r="S11" t="n">
-        <v>491.3887098010809</v>
+        <v>39.33</v>
       </c>
       <c r="T11" t="n">
-        <v>63.06439153642888</v>
+        <v>482.67</v>
       </c>
       <c r="U11" t="n">
-        <v>485.9114206785771</v>
+        <v>58.53</v>
       </c>
       <c r="V11" t="n">
-        <v>70.08377980638812</v>
+        <v>483.44</v>
       </c>
       <c r="W11" t="n">
-        <v>485.6412398547824</v>
+        <v>54.37</v>
       </c>
       <c r="X11" t="n">
-        <v>65.73881757291635</v>
+        <v>490.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>481.0073657523502</v>
+        <v>61.76</v>
       </c>
       <c r="Z11" t="n">
-        <v>68.87902928952924</v>
+        <v>489.67</v>
       </c>
       <c r="AA11" t="n">
+        <v>61.98</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>491.39</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>485.91</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>70.08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>485.64</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>481.01</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>-0.35</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AK11" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AL11" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AM11" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AN11" t="n">
         <v>-0.01666666666666667</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AO11" t="n">
         <v>-0.01428571428571429</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AP11" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AQ11" t="n">
         <v>-0.04444444444444445</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AR11" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AS11" t="n">
         <v>482.95</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>483.5666666666667</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>486.425</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>489.82</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>491.5583333333333</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>491.1357142857143</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>487.975</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>487.4166666666667</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>485.81</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>45.03606887817808</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>50.62587173460709</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>54.77882232213467</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>58.78254502826498</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>60.30337135867465</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>60.72104962323147</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>62.55826783887163</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>64.01405010707502</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>64.33275915115098</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>421</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>396</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>396</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>396</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>396</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>396</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>396</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>396</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>396</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>640</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>640</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>640</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>640</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>640</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>640</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>640</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>640</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>640</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>1</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.72</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.6896551724137931</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.7647058823529411</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>481.01</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>68.88</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>478</v>
       </c>
       <c r="C12" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D12" t="n">
         <v>58</v>
-      </c>
-      <c r="D12" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E12" t="n">
         <v>478</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>456.9527968558469</v>
-      </c>
-      <c r="J12" t="n">
-        <v>67.78776587012968</v>
-      </c>
-      <c r="K12" t="n">
-        <v>469.9002696099931</v>
-      </c>
-      <c r="L12" t="n">
-        <v>58.8033250016958</v>
-      </c>
-      <c r="M12" t="n">
-        <v>475.467978981588</v>
-      </c>
-      <c r="N12" t="n">
-        <v>51.84076934936058</v>
-      </c>
-      <c r="O12" t="n">
-        <v>475.8846557421174</v>
-      </c>
-      <c r="P12" t="n">
-        <v>48.9632860521471</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>475.372095512586</v>
-      </c>
       <c r="R12" t="n">
-        <v>55.03469300931208</v>
+        <v>456.95</v>
       </c>
       <c r="S12" t="n">
-        <v>474.4543087058686</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>53.51887386291195</v>
+        <v>469.9</v>
       </c>
       <c r="U12" t="n">
-        <v>473.3300421519173</v>
+        <v>58.8</v>
       </c>
       <c r="V12" t="n">
-        <v>52.86341798299155</v>
+        <v>475.47</v>
       </c>
       <c r="W12" t="n">
-        <v>468.8013092998377</v>
+        <v>51.84</v>
       </c>
       <c r="X12" t="n">
-        <v>55.36612234374309</v>
+        <v>475.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>469.63117110474</v>
+        <v>48.96</v>
       </c>
       <c r="Z12" t="n">
-        <v>53.57720217751398</v>
+        <v>475.37</v>
       </c>
       <c r="AA12" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>474.45</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>473.33</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>468.8</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>469.63</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>-0.35</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AK12" t="n">
         <v>-0.1666666666666667</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AL12" t="n">
         <v>-0.175</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AM12" t="n">
         <v>-0.1515151515151515</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AN12" t="n">
         <v>-0.1092436974789916</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AO12" t="n">
         <v>-0.07913669064748201</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AP12" t="n">
         <v>-0.06918238993710692</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AQ12" t="n">
         <v>-0.08379888268156424</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AR12" t="n">
         <v>-0.06532663316582915</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AS12" t="n">
         <v>467.3</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>471.15</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>470.8375</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>472.25</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>473.9166666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>474.7214285714286</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>475.0375</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>473.3666666666667</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>473.565</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>68.70014556025336</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>68.71118904516207</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>65.11536756979875</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>61.39110277556512</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>59.59454439982088</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>58.6159495429045</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>57.40240494744101</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>57.06223697760971</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>56.65558908880924</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>365</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>365</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>365</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>365</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>365</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>365</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>365</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>365</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>365</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>645</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>645</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>645</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>645</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>645</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>645</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>645</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>645</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>645</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>1</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>1</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.8695652173913043</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.8620689655172413</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.8529411764705882</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.972972972972973</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>469.63</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>53.58</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>481</v>
       </c>
       <c r="C13" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E13" t="n">
         <v>481</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>532.6922370472724</v>
-      </c>
-      <c r="J13" t="n">
-        <v>28.8842147186521</v>
-      </c>
-      <c r="K13" t="n">
-        <v>515.2483798518242</v>
-      </c>
-      <c r="L13" t="n">
-        <v>68.52463385737811</v>
-      </c>
-      <c r="M13" t="n">
-        <v>508.4120853669255</v>
-      </c>
-      <c r="N13" t="n">
-        <v>61.02102436456729</v>
-      </c>
-      <c r="O13" t="n">
-        <v>495.7536088626623</v>
-      </c>
-      <c r="P13" t="n">
-        <v>77.85775986352795</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>492.6791730561435</v>
-      </c>
       <c r="R13" t="n">
-        <v>77.00575307268785</v>
+        <v>532.6900000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>487.905215314081</v>
+        <v>28.88</v>
       </c>
       <c r="T13" t="n">
-        <v>83.71047370954462</v>
+        <v>515.25</v>
       </c>
       <c r="U13" t="n">
-        <v>486.0421364379573</v>
+        <v>68.52</v>
       </c>
       <c r="V13" t="n">
-        <v>82.58594974009516</v>
+        <v>508.41</v>
       </c>
       <c r="W13" t="n">
-        <v>484.355992047278</v>
+        <v>61.02</v>
       </c>
       <c r="X13" t="n">
-        <v>78.85447205001658</v>
+        <v>495.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>485.9895356288798</v>
+        <v>77.86</v>
       </c>
       <c r="Z13" t="n">
-        <v>72.70258751226962</v>
+        <v>492.68</v>
       </c>
       <c r="AA13" t="n">
+        <v>77.01000000000001</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>487.91</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>83.70999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>486.04</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>484.36</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>485.99</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>0.75</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AK13" t="n">
         <v>0.2</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AL13" t="n">
         <v>0.1</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AM13" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AN13" t="n">
         <v>-0.06666666666666667</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AO13" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AP13" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AQ13" t="n">
         <v>-0.08888888888888889</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AR13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AS13" t="n">
         <v>537.175</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>511.0666666666667</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>509.2375</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>496.76</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>493.9666666666666</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>489.2928571428571</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>487.35</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>487.5277777777778</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>487.335</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>31.92560688538277</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>49.40811899093328</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>57.50440064682007</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>65.71029143140365</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>68.63246721163065</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>74.07327418833052</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>77.8908852177198</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>78.35038329024559</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>77.820259412315</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>483</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>421</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>421</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>393</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>393</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>378</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>369</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>369</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>369</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>651</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>651</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>651</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>651</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>651</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>651</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>651</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>651</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>651</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.625</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>1</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.84</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>485.99</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>72.7</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>482</v>
       </c>
       <c r="C14" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D14" t="n">
         <v>58</v>
-      </c>
-      <c r="D14" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E14" t="n">
         <v>482</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>490.8545021955586</v>
-      </c>
-      <c r="J14" t="n">
-        <v>34.5648767363711</v>
-      </c>
-      <c r="K14" t="n">
-        <v>489.9582388554798</v>
-      </c>
-      <c r="L14" t="n">
-        <v>64.51729459651636</v>
-      </c>
-      <c r="M14" t="n">
-        <v>489.8347598077715</v>
-      </c>
-      <c r="N14" t="n">
-        <v>53.92088024166904</v>
-      </c>
-      <c r="O14" t="n">
-        <v>484.4764027883784</v>
-      </c>
-      <c r="P14" t="n">
-        <v>53.02279657090958</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>486.9812493054942</v>
-      </c>
       <c r="R14" t="n">
-        <v>56.08336753211834</v>
+        <v>490.85</v>
       </c>
       <c r="S14" t="n">
-        <v>486.8652347144055</v>
+        <v>34.56</v>
       </c>
       <c r="T14" t="n">
-        <v>54.43923997104186</v>
+        <v>489.96</v>
       </c>
       <c r="U14" t="n">
-        <v>480.9209135749211</v>
+        <v>64.52</v>
       </c>
       <c r="V14" t="n">
-        <v>66.57868489643143</v>
+        <v>489.83</v>
       </c>
       <c r="W14" t="n">
-        <v>478.3669173357266</v>
+        <v>53.92</v>
       </c>
       <c r="X14" t="n">
-        <v>72.82617652387695</v>
+        <v>484.48</v>
       </c>
       <c r="Y14" t="n">
-        <v>477.1903531998877</v>
+        <v>53.02</v>
       </c>
       <c r="Z14" t="n">
-        <v>70.86834843638788</v>
+        <v>486.98</v>
       </c>
       <c r="AA14" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>486.87</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>54.44</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>480.92</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>66.58</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>478.37</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>72.83</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>477.19</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>-0.2307692307692308</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AK14" t="n">
         <v>-0.1186440677966102</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AL14" t="n">
         <v>-0.08860759493670886</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AM14" t="n">
         <v>-0.0707070707070707</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AN14" t="n">
         <v>-0.05882352941176471</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AO14" t="n">
         <v>-0.05035971223021583</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AP14" t="n">
         <v>-0.1069182389937107</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AQ14" t="n">
         <v>-0.1173184357541899</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AR14" t="n">
         <v>-0.1155778894472362</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AS14" t="n">
         <v>485.6</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>489.2833333333334</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>489.1875</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>488.55</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>488.5416666666667</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>488.15</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>482.75</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>480.1444444444444</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>478.835</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>35.07834089577214</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>48.89311187569154</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>54.83705265374863</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>55.60258537154545</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>56.40920371613917</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>55.95213834800494</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>58.12970411072122</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>60.46818467611452</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>62.79369215932441</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>353</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>353</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>353</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>353</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>353</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>353</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>353</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>353</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>353</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BT14" t="n">
         <v>534</v>
       </c>
-      <c r="BL14" t="n">
+      <c r="BU14" t="n">
         <v>569</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BV14" t="n">
         <v>575</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BW14" t="n">
         <v>575</v>
       </c>
-      <c r="BO14" t="n">
+      <c r="BX14" t="n">
         <v>575</v>
       </c>
-      <c r="BP14" t="n">
+      <c r="BY14" t="n">
         <v>575</v>
       </c>
-      <c r="BQ14" t="n">
+      <c r="BZ14" t="n">
         <v>575</v>
       </c>
-      <c r="BR14" t="n">
+      <c r="CA14" t="n">
         <v>575</v>
       </c>
-      <c r="BS14" t="n">
+      <c r="CB14" t="n">
         <v>575</v>
       </c>
-      <c r="BT14" t="n">
+      <c r="CC14" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>1</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.75</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.45</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.9</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>0.72</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.6428571428571429</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>477.19</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>70.87</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>478</v>
       </c>
       <c r="C15" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D15" t="n">
         <v>59</v>
-      </c>
-      <c r="D15" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E15" t="n">
         <v>478</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>467.226868591247</v>
-      </c>
-      <c r="J15" t="n">
-        <v>37.94102534887034</v>
-      </c>
-      <c r="K15" t="n">
-        <v>480.5903655011353</v>
-      </c>
-      <c r="L15" t="n">
-        <v>64.83761887358956</v>
-      </c>
-      <c r="M15" t="n">
-        <v>483.8585829747972</v>
-      </c>
-      <c r="N15" t="n">
-        <v>55.61853520238548</v>
-      </c>
-      <c r="O15" t="n">
-        <v>482.8593701303149</v>
-      </c>
-      <c r="P15" t="n">
-        <v>64.83670408877204</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>480.733477848597</v>
-      </c>
       <c r="R15" t="n">
-        <v>61.96033320590566</v>
+        <v>467.23</v>
       </c>
       <c r="S15" t="n">
-        <v>474.0659906433188</v>
+        <v>37.94</v>
       </c>
       <c r="T15" t="n">
-        <v>69.30014720657161</v>
+        <v>480.59</v>
       </c>
       <c r="U15" t="n">
-        <v>480.3625449840132</v>
+        <v>64.84</v>
       </c>
       <c r="V15" t="n">
-        <v>68.29840447412597</v>
+        <v>483.86</v>
       </c>
       <c r="W15" t="n">
-        <v>477.0058527384826</v>
+        <v>55.62</v>
       </c>
       <c r="X15" t="n">
-        <v>63.79157603056884</v>
+        <v>482.86</v>
       </c>
       <c r="Y15" t="n">
-        <v>474.8940985383438</v>
+        <v>64.84</v>
       </c>
       <c r="Z15" t="n">
-        <v>61.90036234127173</v>
+        <v>480.73</v>
       </c>
       <c r="AA15" t="n">
+        <v>61.96</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>474.07</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>480.36</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>477.01</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>63.79</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>474.89</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AK15" t="n">
         <v>-0.2333333333333333</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AL15" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AM15" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AN15" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AO15" t="n">
         <v>-0.1285714285714286</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AP15" t="n">
         <v>-0.08749999999999999</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AQ15" t="n">
         <v>-0.07777777777777778</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AR15" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AS15" t="n">
         <v>464.65</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>485.35</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>489.375</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>485.04</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>482.6</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>478.3285714285714</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>480.09375</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>479.9</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>480.045</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>31.30938357745166</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>52.07905049057635</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>57.32895756073016</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>60.18985296542931</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>62.43748873873773</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>64.33832926215055</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>64.96131511089888</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>64.85112009655482</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>64.46047606867327</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>373</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>373</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>373</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>373</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>373</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>373</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>373</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>373</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>373</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BT15" t="n">
         <v>536</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BU15" t="n">
         <v>579</v>
       </c>
-      <c r="BM15" t="n">
+      <c r="BV15" t="n">
         <v>579</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="BW15" t="n">
         <v>579</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BX15" t="n">
         <v>579</v>
       </c>
-      <c r="BP15" t="n">
+      <c r="BY15" t="n">
         <v>579</v>
       </c>
-      <c r="BQ15" t="n">
+      <c r="BZ15" t="n">
         <v>579</v>
       </c>
-      <c r="BR15" t="n">
+      <c r="CA15" t="n">
         <v>579</v>
       </c>
-      <c r="BS15" t="n">
+      <c r="CB15" t="n">
         <v>579</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="CC15" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.8</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.84</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.8518518518518519</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>474.89</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>61.9</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>481</v>
       </c>
       <c r="C16" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D16" t="n">
         <v>59</v>
-      </c>
-      <c r="D16" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E16" t="n">
         <v>481</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>467.7253208763755</v>
-      </c>
-      <c r="J16" t="n">
-        <v>61.24914221602341</v>
-      </c>
-      <c r="K16" t="n">
-        <v>481.6761554919973</v>
-      </c>
-      <c r="L16" t="n">
-        <v>63.6155014065586</v>
-      </c>
-      <c r="M16" t="n">
-        <v>479.2557197246018</v>
-      </c>
-      <c r="N16" t="n">
-        <v>65.56709330472165</v>
-      </c>
-      <c r="O16" t="n">
-        <v>473.6375220660298</v>
-      </c>
-      <c r="P16" t="n">
-        <v>65.09955732278124</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>472.7484928433709</v>
-      </c>
       <c r="R16" t="n">
-        <v>62.6732224067416</v>
+        <v>467.73</v>
       </c>
       <c r="S16" t="n">
-        <v>476.176456035942</v>
+        <v>61.25</v>
       </c>
       <c r="T16" t="n">
-        <v>66.2293404967462</v>
+        <v>481.68</v>
       </c>
       <c r="U16" t="n">
-        <v>475.6726260942605</v>
+        <v>63.62</v>
       </c>
       <c r="V16" t="n">
-        <v>61.8098624625996</v>
+        <v>479.26</v>
       </c>
       <c r="W16" t="n">
-        <v>477.0966675200265</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>62.04685368673022</v>
+        <v>473.64</v>
       </c>
       <c r="Y16" t="n">
-        <v>478.2662844942481</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>62.08012960102273</v>
+        <v>472.75</v>
       </c>
       <c r="AA16" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>476.18</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>475.67</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>477.1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>478.27</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>-0.0847457627118644</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AL16" t="n">
         <v>-0.08860759493670886</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AM16" t="n">
         <v>-0.0707070707070707</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AN16" t="n">
         <v>-0.05882352941176471</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AO16" t="n">
         <v>-0.03597122302158273</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AP16" t="n">
         <v>-0.03144654088050314</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AQ16" t="n">
         <v>-0.02793296089385475</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AR16" t="n">
         <v>-0.02512562814070352</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AS16" t="n">
         <v>469.175</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>481.35</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>479.325</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>479.36</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>477.5083333333333</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>478.0857142857143</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>477.2625</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>476.9833333333333</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>476.805</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>60.45324122824184</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>63.7110207630255</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>64.6938511374922</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>65.47786190767074</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>64.26131493536545</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>64.40058625668</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>64.17919128307867</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>63.74284055658504</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>63.06510108609991</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>370</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>370</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>370</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>370</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>370</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>370</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>370</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>370</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>370</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BT16" t="n">
         <v>649</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BU16" t="n">
         <v>649</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BV16" t="n">
         <v>649</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>649</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BX16" t="n">
         <v>649</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BY16" t="n">
         <v>649</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BZ16" t="n">
         <v>649</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="CA16" t="n">
         <v>649</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="CB16" t="n">
         <v>649</v>
       </c>
-      <c r="BT16" t="n">
+      <c r="CC16" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.7037037037037037</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.8235294117647058</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.8378378378378378</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.85</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>478.27</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>62.08</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>480</v>
       </c>
       <c r="C17" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D17" t="n">
         <v>59</v>
-      </c>
-      <c r="D17" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E17" t="n">
         <v>480</v>
@@ -4542,228 +5092,261 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>494.2116925304808</v>
-      </c>
-      <c r="J17" t="n">
-        <v>62.37132754159774</v>
-      </c>
-      <c r="K17" t="n">
-        <v>491.2768062696371</v>
-      </c>
-      <c r="L17" t="n">
-        <v>70.958309335626</v>
-      </c>
-      <c r="M17" t="n">
-        <v>492.3359392016263</v>
-      </c>
-      <c r="N17" t="n">
-        <v>59.42766071102302</v>
-      </c>
-      <c r="O17" t="n">
-        <v>488.3747103018407</v>
-      </c>
-      <c r="P17" t="n">
-        <v>59.36928291119665</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>489.0326914303425</v>
-      </c>
       <c r="R17" t="n">
-        <v>65.20259212955501</v>
+        <v>494.21</v>
       </c>
       <c r="S17" t="n">
-        <v>489.4572763238449</v>
+        <v>62.37</v>
       </c>
       <c r="T17" t="n">
-        <v>70.80628050101444</v>
+        <v>491.28</v>
       </c>
       <c r="U17" t="n">
-        <v>485.1667784735296</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>66.2206490973081</v>
+        <v>492.34</v>
       </c>
       <c r="W17" t="n">
-        <v>486.6733757426705</v>
+        <v>59.43</v>
       </c>
       <c r="X17" t="n">
-        <v>67.67128583420886</v>
+        <v>488.37</v>
       </c>
       <c r="Y17" t="n">
-        <v>485.8525950479294</v>
+        <v>59.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>68.30950043870507</v>
+        <v>489.03</v>
       </c>
       <c r="AA17" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>489.46</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>70.81</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>485.17</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>66.22</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>486.67</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>67.67</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>485.85</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>68.31</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AK17" t="n">
         <v>-0.06666666666666667</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AL17" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AM17" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AN17" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AO17" t="n">
         <v>-0.04285714285714286</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AP17" t="n">
         <v>-0.0375</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AQ17" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AR17" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AS17" t="n">
         <v>492.8</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>490.7833333333334</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>491.95</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>490.77</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>491.175</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>489.4714285714286</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>488.68125</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>488.1944444444445</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>488.495</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>54.74586742394352</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>59.88547171244643</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>62.70384756934777</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>61.60387244321577</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>61.89058389609844</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>63.46297490406095</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>65.24543775956676</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>65.57981542637967</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>66.61253617000332</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>358</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>358</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>358</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>358</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>358</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>358</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>358</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>358</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>358</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BT17" t="n">
         <v>578</v>
       </c>
-      <c r="BL17" t="n">
+      <c r="BU17" t="n">
         <v>584</v>
       </c>
-      <c r="BM17" t="n">
+      <c r="BV17" t="n">
         <v>584</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BW17" t="n">
         <v>584</v>
       </c>
-      <c r="BO17" t="n">
+      <c r="BX17" t="n">
         <v>584</v>
       </c>
-      <c r="BP17" t="n">
+      <c r="BY17" t="n">
         <v>584</v>
       </c>
-      <c r="BQ17" t="n">
+      <c r="BZ17" t="n">
         <v>584</v>
       </c>
-      <c r="BR17" t="n">
+      <c r="CA17" t="n">
         <v>584</v>
       </c>
-      <c r="BS17" t="n">
+      <c r="CB17" t="n">
         <v>584</v>
       </c>
-      <c r="BT17" t="n">
+      <c r="CC17" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>1</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.3157894736842105</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.7941176470588235</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>485.85</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>68.31</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>478</v>
       </c>
       <c r="C18" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D18" t="n">
         <v>62</v>
-      </c>
-      <c r="D18" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E18" t="n">
         <v>478</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>461.22145814248</v>
-      </c>
-      <c r="J18" t="n">
-        <v>67.93473756746741</v>
-      </c>
-      <c r="K18" t="n">
-        <v>466.455382478388</v>
-      </c>
-      <c r="L18" t="n">
-        <v>77.16481341093524</v>
-      </c>
-      <c r="M18" t="n">
-        <v>472.9277974615656</v>
-      </c>
-      <c r="N18" t="n">
-        <v>74.25168249959366</v>
-      </c>
-      <c r="O18" t="n">
-        <v>477.8690486090209</v>
-      </c>
-      <c r="P18" t="n">
-        <v>85.3910352860467</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>479.422547220844</v>
-      </c>
       <c r="R18" t="n">
-        <v>77.24351636652297</v>
+        <v>461.22</v>
       </c>
       <c r="S18" t="n">
-        <v>475.0591047092767</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>75.80422989780081</v>
+        <v>466.46</v>
       </c>
       <c r="U18" t="n">
-        <v>474.3802313889726</v>
+        <v>77.16</v>
       </c>
       <c r="V18" t="n">
-        <v>75.55540740654853</v>
+        <v>472.93</v>
       </c>
       <c r="W18" t="n">
-        <v>471.8963291044255</v>
+        <v>74.25</v>
       </c>
       <c r="X18" t="n">
-        <v>71.99155763844696</v>
+        <v>477.87</v>
       </c>
       <c r="Y18" t="n">
-        <v>477.7492862988611</v>
+        <v>85.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>69.42965148263261</v>
+        <v>479.42</v>
       </c>
       <c r="AA18" t="n">
+        <v>77.23999999999999</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>475.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>474.38</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>75.56</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>471.9</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>477.75</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>69.43000000000001</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>-0.2307692307692308</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AK18" t="n">
         <v>-0.1186440677966102</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AL18" t="n">
         <v>-0.06329113924050633</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AM18" t="n">
         <v>-0.0101010101010101</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AN18" t="n">
         <v>-0.02521008403361345</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AO18" t="n">
         <v>-0.02158273381294964</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AP18" t="n">
         <v>-0.01886792452830189</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AQ18" t="n">
         <v>-0.00558659217877095</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AR18" t="n">
         <v>-0.01507537688442211</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AS18" t="n">
         <v>469.875</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>472.3833333333333</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>473.0625</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>477.53</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>476.625</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>477.4285714285714</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>476.45625</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>477.05</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>476.155</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>59.38189433657367</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>66.62909566314771</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>68.91559035334458</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>73.36667567772169</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>75.63311251253205</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>75.27512801689004</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>75.11947541042537</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>74.03034475432655</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>72.83701651632911</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>390</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>382</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>375</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>369</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>369</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>369</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>369</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>369</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>369</v>
       </c>
-      <c r="BK18" t="n">
+      <c r="BT18" t="n">
         <v>633</v>
       </c>
-      <c r="BL18" t="n">
+      <c r="BU18" t="n">
         <v>633</v>
       </c>
-      <c r="BM18" t="n">
+      <c r="BV18" t="n">
         <v>633</v>
       </c>
-      <c r="BN18" t="n">
+      <c r="BW18" t="n">
         <v>633</v>
       </c>
-      <c r="BO18" t="n">
+      <c r="BX18" t="n">
         <v>633</v>
       </c>
-      <c r="BP18" t="n">
+      <c r="BY18" t="n">
         <v>633</v>
       </c>
-      <c r="BQ18" t="n">
+      <c r="BZ18" t="n">
         <v>633</v>
       </c>
-      <c r="BR18" t="n">
+      <c r="CA18" t="n">
         <v>633</v>
       </c>
-      <c r="BS18" t="n">
+      <c r="CB18" t="n">
         <v>633</v>
       </c>
-      <c r="BT18" t="n">
+      <c r="CC18" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>1</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.9090909090909091</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>477.75</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>69.43000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>480</v>
       </c>
       <c r="C19" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D19" t="n">
         <v>61</v>
-      </c>
-      <c r="D19" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E19" t="n">
         <v>480</v>
@@ -5034,720 +5650,819 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>469.6329006935276</v>
-      </c>
-      <c r="J19" t="n">
-        <v>82.69164600746782</v>
-      </c>
-      <c r="K19" t="n">
-        <v>460.5925495598096</v>
-      </c>
-      <c r="L19" t="n">
-        <v>94.81406064079127</v>
-      </c>
-      <c r="M19" t="n">
-        <v>465.2908826205789</v>
-      </c>
-      <c r="N19" t="n">
-        <v>86.05278571878681</v>
-      </c>
-      <c r="O19" t="n">
-        <v>469.8598574613246</v>
-      </c>
-      <c r="P19" t="n">
-        <v>95.6538204636643</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>478.1412181813125</v>
-      </c>
       <c r="R19" t="n">
-        <v>100.4021312527317</v>
+        <v>469.63</v>
       </c>
       <c r="S19" t="n">
-        <v>475.3798191765175</v>
+        <v>82.69</v>
       </c>
       <c r="T19" t="n">
-        <v>87.12467398509985</v>
+        <v>460.59</v>
       </c>
       <c r="U19" t="n">
-        <v>476.5685708089924</v>
+        <v>94.81</v>
       </c>
       <c r="V19" t="n">
-        <v>85.94076059584384</v>
+        <v>465.29</v>
       </c>
       <c r="W19" t="n">
-        <v>479.0332281656921</v>
+        <v>86.05</v>
       </c>
       <c r="X19" t="n">
-        <v>82.80167274251187</v>
+        <v>469.86</v>
       </c>
       <c r="Y19" t="n">
-        <v>481.8374518469683</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="Z19" t="n">
-        <v>82.98929944581111</v>
+        <v>478.14</v>
       </c>
       <c r="AA19" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>475.38</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>87.12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>476.57</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>479.03</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>481.84</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AK19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AL19" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AM19" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AN19" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AO19" t="n">
         <v>-0.04285714285714286</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AP19" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AQ19" t="n">
         <v>-0.04444444444444445</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AR19" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AS19" t="n">
         <v>459</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>459.6333333333333</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>460.175</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>465.11</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>467.3666666666667</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>469.1142857142857</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>469.04375</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>470.3277777777778</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>470.57</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>70.10848736066126</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>73.0905754678551</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>76.63840013335351</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>79.62247107443977</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>82.72665162382005</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>84.30472666924145</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>84.55474165259746</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>84.28554842225034</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>83.24803361041027</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>285</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>285</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>285</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>285</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>285</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>285</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>285</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>285</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>285</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BT19" t="n">
         <v>550</v>
       </c>
-      <c r="BL19" t="n">
+      <c r="BU19" t="n">
         <v>565</v>
       </c>
-      <c r="BM19" t="n">
+      <c r="BV19" t="n">
         <v>565</v>
       </c>
-      <c r="BN19" t="n">
+      <c r="BW19" t="n">
         <v>573</v>
       </c>
-      <c r="BO19" t="n">
+      <c r="BX19" t="n">
         <v>580</v>
       </c>
-      <c r="BP19" t="n">
+      <c r="BY19" t="n">
         <v>581</v>
       </c>
-      <c r="BQ19" t="n">
+      <c r="BZ19" t="n">
         <v>581</v>
       </c>
-      <c r="BR19" t="n">
+      <c r="CA19" t="n">
         <v>581</v>
       </c>
-      <c r="BS19" t="n">
+      <c r="CB19" t="n">
         <v>581</v>
       </c>
-      <c r="BT19" t="n">
+      <c r="CC19" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>1</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.8260869565217391</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.7037037037037037</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.8235294117647058</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.8823529411764706</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>481.84</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>82.98999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S20_G3_478_61_ABS1</t>
+          <t>S19_G3_481_60_ABS1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D20" t="n">
-        <v>90.43736100815418</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F20" t="n">
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>469.9728743453865</v>
-      </c>
-      <c r="J20" t="n">
-        <v>69.2059250227793</v>
-      </c>
-      <c r="K20" t="n">
-        <v>451.7355540447626</v>
-      </c>
-      <c r="L20" t="n">
-        <v>106.9676458426966</v>
-      </c>
-      <c r="M20" t="n">
-        <v>455.202605759814</v>
-      </c>
-      <c r="N20" t="n">
-        <v>129.5267770900781</v>
-      </c>
-      <c r="O20" t="n">
-        <v>456.9361790772766</v>
-      </c>
-      <c r="P20" t="n">
-        <v>87.78705054171488</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>463.3295597842024</v>
-      </c>
       <c r="R20" t="n">
-        <v>92.17779892349427</v>
+        <v>490.78</v>
       </c>
       <c r="S20" t="n">
-        <v>466.7110691305197</v>
+        <v>51.55</v>
       </c>
       <c r="T20" t="n">
-        <v>88.5856043258237</v>
+        <v>483.63</v>
       </c>
       <c r="U20" t="n">
-        <v>470.6714962514225</v>
+        <v>49.25</v>
       </c>
       <c r="V20" t="n">
-        <v>88.72270893431208</v>
+        <v>464.96</v>
       </c>
       <c r="W20" t="n">
-        <v>471.5023365928234</v>
+        <v>65.13</v>
       </c>
       <c r="X20" t="n">
-        <v>80.19412692499544</v>
+        <v>455.84</v>
       </c>
       <c r="Y20" t="n">
-        <v>464.8782108702229</v>
+        <v>68.02</v>
       </c>
       <c r="Z20" t="n">
-        <v>77.05713075004572</v>
+        <v>461.42</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.5384615384615384</v>
+        <v>64.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.6271186440677966</v>
+        <v>471.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.4430379746835443</v>
+        <v>66.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.3737373737373738</v>
+        <v>476.05</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.2605042016806723</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.223021582733813</v>
+        <v>483.26</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.1823899371069182</v>
+        <v>71.56</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.1955307262569832</v>
+        <v>480.78</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.1658291457286432</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AJ20" t="n">
-        <v>482.35</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>451.8</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>455.2875</v>
+        <v>-0.15</v>
       </c>
       <c r="AM20" t="n">
-        <v>453.73</v>
+        <v>-0.2</v>
       </c>
       <c r="AN20" t="n">
-        <v>459.9333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="AO20" t="n">
-        <v>461.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AP20" t="n">
-        <v>463.35625</v>
+        <v>-0.0625</v>
       </c>
       <c r="AQ20" t="n">
-        <v>461.9722222222222</v>
+        <v>-0.02222222222222222</v>
       </c>
       <c r="AR20" t="n">
-        <v>463.25</v>
+        <v>-0.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>39.11812239870416</v>
+        <v>489.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>62.23552040434787</v>
+        <v>490.5833333333333</v>
       </c>
       <c r="AU20" t="n">
-        <v>71.13775259136318</v>
+        <v>475.875</v>
       </c>
       <c r="AV20" t="n">
-        <v>76.76129949395073</v>
+        <v>465.47</v>
       </c>
       <c r="AW20" t="n">
-        <v>80.11457767195402</v>
+        <v>466.45</v>
       </c>
       <c r="AX20" t="n">
-        <v>82.40723789293546</v>
+        <v>467.5785714285714</v>
       </c>
       <c r="AY20" t="n">
-        <v>83.9276732427243</v>
+        <v>470.04375</v>
       </c>
       <c r="AZ20" t="n">
-        <v>83.23483716139505</v>
+        <v>474.0111111111111</v>
       </c>
       <c r="BA20" t="n">
-        <v>82.04606937568673</v>
+        <v>474.175</v>
       </c>
       <c r="BB20" t="n">
-        <v>413</v>
+        <v>54.99536344093018</v>
       </c>
       <c r="BC20" t="n">
-        <v>354</v>
+        <v>56.15997734646584</v>
       </c>
       <c r="BD20" t="n">
-        <v>351</v>
+        <v>60.74915122863857</v>
       </c>
       <c r="BE20" t="n">
-        <v>345</v>
+        <v>66.22513948645182</v>
       </c>
       <c r="BF20" t="n">
-        <v>345</v>
+        <v>67.25001239157258</v>
       </c>
       <c r="BG20" t="n">
-        <v>345</v>
+        <v>67.07608343804634</v>
       </c>
       <c r="BH20" t="n">
-        <v>345</v>
+        <v>67.50595778105441</v>
       </c>
       <c r="BI20" t="n">
-        <v>345</v>
+        <v>69.24096322015113</v>
       </c>
       <c r="BJ20" t="n">
-        <v>345</v>
+        <v>69.45274922564261</v>
       </c>
       <c r="BK20" t="n">
-        <v>642</v>
+        <v>347</v>
       </c>
       <c r="BL20" t="n">
-        <v>642</v>
+        <v>347</v>
       </c>
       <c r="BM20" t="n">
-        <v>642</v>
+        <v>347</v>
       </c>
       <c r="BN20" t="n">
-        <v>642</v>
+        <v>347</v>
       </c>
       <c r="BO20" t="n">
-        <v>642</v>
+        <v>347</v>
       </c>
       <c r="BP20" t="n">
-        <v>642</v>
+        <v>347</v>
       </c>
       <c r="BQ20" t="n">
-        <v>642</v>
+        <v>347</v>
       </c>
       <c r="BR20" t="n">
-        <v>642</v>
+        <v>347</v>
       </c>
       <c r="BS20" t="n">
-        <v>642</v>
+        <v>347</v>
       </c>
       <c r="BT20" t="n">
-        <v>0.1</v>
+        <v>601</v>
       </c>
       <c r="BU20" t="n">
-        <v>0.5</v>
+        <v>601</v>
       </c>
       <c r="BV20" t="n">
+        <v>601</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>601</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>601</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>601</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>601</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>601</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>601</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CH20" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BW20" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>0.9310344827586207</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>0.84375</v>
-      </c>
-      <c r="CB20" t="n">
-        <v>0.84375</v>
+      <c r="CI20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>480.78</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S19_G3_481_60_ABS1</t>
+          <t>S20_G3_478_61_ABS1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C21" t="n">
-        <v>60</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D21" t="n">
-        <v>88.95478131949592</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F21" t="n">
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>490.7757945083396</v>
-      </c>
-      <c r="J21" t="n">
-        <v>51.55448744056734</v>
-      </c>
-      <c r="K21" t="n">
-        <v>483.6308243443915</v>
-      </c>
-      <c r="L21" t="n">
-        <v>49.25105021765908</v>
-      </c>
-      <c r="M21" t="n">
-        <v>464.9638989973207</v>
-      </c>
-      <c r="N21" t="n">
-        <v>65.12558429227754</v>
-      </c>
-      <c r="O21" t="n">
-        <v>455.8352986141882</v>
-      </c>
-      <c r="P21" t="n">
-        <v>68.01582140612327</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>461.4243383959578</v>
-      </c>
       <c r="R21" t="n">
-        <v>64.87879447257303</v>
+        <v>469.97</v>
       </c>
       <c r="S21" t="n">
-        <v>471.7740415567474</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>66.41595691954544</v>
+        <v>451.74</v>
       </c>
       <c r="U21" t="n">
-        <v>476.0488338322073</v>
+        <v>106.97</v>
       </c>
       <c r="V21" t="n">
-        <v>68.35033550434017</v>
+        <v>455.2</v>
       </c>
       <c r="W21" t="n">
-        <v>483.2570494861553</v>
+        <v>129.53</v>
       </c>
       <c r="X21" t="n">
-        <v>71.56051851911124</v>
+        <v>456.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>480.7766140653601</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="Z21" t="n">
-        <v>70.39512173552092</v>
+        <v>463.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>466.71</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.15</v>
+        <v>88.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.2</v>
+        <v>470.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.1333333333333333</v>
+        <v>88.72</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.1</v>
+        <v>471.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.0625</v>
+        <v>80.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.02222222222222222</v>
+        <v>464.88</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.03</v>
+        <v>77.06</v>
       </c>
       <c r="AJ21" t="n">
-        <v>489.9</v>
+        <v>-0.5384615384615384</v>
       </c>
       <c r="AK21" t="n">
-        <v>490.5833333333333</v>
+        <v>-0.6271186440677966</v>
       </c>
       <c r="AL21" t="n">
-        <v>475.875</v>
+        <v>-0.4430379746835443</v>
       </c>
       <c r="AM21" t="n">
-        <v>465.47</v>
+        <v>-0.3737373737373738</v>
       </c>
       <c r="AN21" t="n">
-        <v>466.45</v>
+        <v>-0.2605042016806723</v>
       </c>
       <c r="AO21" t="n">
-        <v>467.5785714285714</v>
+        <v>-0.223021582733813</v>
       </c>
       <c r="AP21" t="n">
-        <v>470.04375</v>
+        <v>-0.1823899371069182</v>
       </c>
       <c r="AQ21" t="n">
-        <v>474.0111111111111</v>
+        <v>-0.1955307262569832</v>
       </c>
       <c r="AR21" t="n">
-        <v>474.175</v>
+        <v>-0.1658291457286432</v>
       </c>
       <c r="AS21" t="n">
-        <v>54.99536344093018</v>
+        <v>482.35</v>
       </c>
       <c r="AT21" t="n">
-        <v>56.15997734646584</v>
+        <v>451.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>60.74915122863857</v>
+        <v>455.2875</v>
       </c>
       <c r="AV21" t="n">
-        <v>66.22513948645182</v>
+        <v>453.73</v>
       </c>
       <c r="AW21" t="n">
-        <v>67.25001239157258</v>
+        <v>459.9333333333333</v>
       </c>
       <c r="AX21" t="n">
-        <v>67.07608343804634</v>
+        <v>461.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>67.50595778105441</v>
+        <v>463.35625</v>
       </c>
       <c r="AZ21" t="n">
-        <v>69.24096322015113</v>
+        <v>461.9722222222222</v>
       </c>
       <c r="BA21" t="n">
-        <v>69.45274922564261</v>
+        <v>463.25</v>
       </c>
       <c r="BB21" t="n">
-        <v>347</v>
+        <v>39.11812239870416</v>
       </c>
       <c r="BC21" t="n">
-        <v>347</v>
+        <v>62.23552040434787</v>
       </c>
       <c r="BD21" t="n">
-        <v>347</v>
+        <v>71.13775259136318</v>
       </c>
       <c r="BE21" t="n">
-        <v>347</v>
+        <v>76.76129949395073</v>
       </c>
       <c r="BF21" t="n">
-        <v>347</v>
+        <v>80.11457767195402</v>
       </c>
       <c r="BG21" t="n">
-        <v>347</v>
+        <v>82.40723789293546</v>
       </c>
       <c r="BH21" t="n">
-        <v>347</v>
+        <v>83.9276732427243</v>
       </c>
       <c r="BI21" t="n">
-        <v>347</v>
+        <v>83.23483716139505</v>
       </c>
       <c r="BJ21" t="n">
-        <v>347</v>
+        <v>82.04606937568673</v>
       </c>
       <c r="BK21" t="n">
-        <v>601</v>
+        <v>413</v>
       </c>
       <c r="BL21" t="n">
-        <v>601</v>
+        <v>354</v>
       </c>
       <c r="BM21" t="n">
-        <v>601</v>
+        <v>351</v>
       </c>
       <c r="BN21" t="n">
-        <v>601</v>
+        <v>345</v>
       </c>
       <c r="BO21" t="n">
-        <v>601</v>
+        <v>345</v>
       </c>
       <c r="BP21" t="n">
-        <v>601</v>
+        <v>345</v>
       </c>
       <c r="BQ21" t="n">
-        <v>601</v>
+        <v>345</v>
       </c>
       <c r="BR21" t="n">
-        <v>601</v>
+        <v>345</v>
       </c>
       <c r="BS21" t="n">
-        <v>601</v>
+        <v>345</v>
       </c>
       <c r="BT21" t="n">
-        <v>1</v>
+        <v>642</v>
       </c>
       <c r="BU21" t="n">
-        <v>0.8</v>
+        <v>642</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.9</v>
+        <v>642</v>
       </c>
       <c r="BW21" t="n">
-        <v>1</v>
+        <v>642</v>
       </c>
       <c r="BX21" t="n">
-        <v>0.8571428571428571</v>
+        <v>642</v>
       </c>
       <c r="BY21" t="n">
+        <v>642</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>642</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>642</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>642</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CE21" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BZ21" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="CB21" t="n">
-        <v>0.3846153846153846</v>
+      <c r="CF21" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>464.88</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>77.06</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>479.2</v>
       </c>
       <c r="C22" t="n">
+        <v>88.28762045959969</v>
+      </c>
+      <c r="D22" t="n">
         <v>59.55</v>
-      </c>
-      <c r="D22" t="n">
-        <v>88.28762045959969</v>
       </c>
       <c r="E22" t="n">
         <v>479.2</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.50025</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>76.075</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.8305</v>
+      </c>
       <c r="I22" t="n">
-        <v>482.1400274643135</v>
+        <v>2.8005</v>
       </c>
       <c r="J22" t="n">
-        <v>57.19355302593622</v>
+        <v>2.7685</v>
       </c>
       <c r="K22" t="n">
-        <v>480.9510934546376</v>
+        <v>2.7475</v>
       </c>
       <c r="L22" t="n">
-        <v>66.50733377901267</v>
+        <v>2.7375</v>
       </c>
       <c r="M22" t="n">
-        <v>480.0632101811423</v>
+        <v>2.733</v>
       </c>
       <c r="N22" t="n">
-        <v>66.17591001304123</v>
+        <v>2.7495</v>
       </c>
       <c r="O22" t="n">
-        <v>479.1039211600452</v>
+        <v>2.8295</v>
       </c>
       <c r="P22" t="n">
-        <v>68.64844908842157</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>479.605666345341</v>
-      </c>
+        <v>2.8435</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>69.99798271955783</v>
+        <v>482.14</v>
       </c>
       <c r="S22" t="n">
-        <v>479.5459538885058</v>
+        <v>57.19250000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>70.59541195369422</v>
+        <v>480.9519999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>480.0803455479299</v>
+        <v>66.50700000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>70.98484403148595</v>
+        <v>480.0635</v>
       </c>
       <c r="W22" t="n">
-        <v>480.0316207540126</v>
+        <v>66.17599999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>70.63875063033166</v>
+        <v>479.1050000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>479.1348999559654</v>
+        <v>68.64800000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>70.62510535635343</v>
+        <v>479.605</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.158974358974359</v>
+        <v>69.99850000000001</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.1324858757062147</v>
+        <v>479.546</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.1213291139240506</v>
+        <v>70.59599999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.1152863327149042</v>
+        <v>480.08</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.09179461615154537</v>
+        <v>70.985</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.08000610691570968</v>
+        <v>480.033</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.07121915054533876</v>
+        <v>70.63799999999999</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.06106497464761227</v>
+        <v>479.1355</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.05992987665600731</v>
+        <v>70.62450000000001</v>
       </c>
       <c r="AJ22" t="n">
-        <v>484.635</v>
+        <v>-0.1585</v>
       </c>
       <c r="AK22" t="n">
-        <v>482.34</v>
+        <v>-0.1335</v>
       </c>
       <c r="AL22" t="n">
-        <v>481.054375</v>
+        <v>-0.121</v>
       </c>
       <c r="AM22" t="n">
+        <v>-0.115</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.09150000000000001</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-0.0605</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>-0.0615</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>484.636</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>482.3394999999999</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>481.055</v>
+      </c>
+      <c r="AV22" t="n">
         <v>479.2395</v>
       </c>
-      <c r="AN22" t="n">
-        <v>479.58875</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>479.4542857142857</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>479.3190625000001</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>479.6311111111111</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>479.24225</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>51.87035648974675</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>58.0856775321923</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>61.21186490032837</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>64.15414677352366</v>
-      </c>
       <c r="AW22" t="n">
-        <v>65.89217758345742</v>
+        <v>479.5900000000001</v>
       </c>
       <c r="AX22" t="n">
-        <v>67.35494945354485</v>
+        <v>479.455</v>
       </c>
       <c r="AY22" t="n">
-        <v>68.3392413575436</v>
+        <v>479.3190000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>68.83713592036619</v>
+        <v>479.6315000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>69.07657142932756</v>
+        <v>479.2425</v>
       </c>
       <c r="BB22" t="n">
+        <v>51.87149999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>58.086</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>61.2115</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>64.15400000000001</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>65.89149999999999</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>67.3545</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>68.339</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>68.83599999999998</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>69.07699999999998</v>
+      </c>
+      <c r="BK22" t="n">
         <v>382.15</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>371.85</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>367.8</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>362.2</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>361.85</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>360.85</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>360.4</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>360.4</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>360.4</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>609.15</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>615.15</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>615.55</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>616.1</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>616.65</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>616.7</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>617.35</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>618.95</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>619.25</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6122023809523809</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.6600729825729825</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7412270490946962</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.8859919002566061</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.8193274049346704</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.7223471589879429</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.7585147398289651</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8203364090198123</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.779030188813277</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>479.1355</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>70.62450000000001</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.399247918291146</v>
       </c>
       <c r="C23" t="n">
+        <v>1.765715096979629</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.190974832912761</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.765715096979629</v>
       </c>
       <c r="E23" t="n">
         <v>1.399247918291146</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01585086748414737</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.48035379839451</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1922026069158875</v>
+      </c>
       <c r="I23" t="n">
-        <v>22.53864529049362</v>
+        <v>0.1974968354176846</v>
       </c>
       <c r="J23" t="n">
-        <v>22.818443157537</v>
+        <v>0.2068122718541472</v>
       </c>
       <c r="K23" t="n">
-        <v>19.00327745555509</v>
+        <v>0.1961705756142905</v>
       </c>
       <c r="L23" t="n">
-        <v>21.09594916954241</v>
+        <v>0.204653108299977</v>
       </c>
       <c r="M23" t="n">
-        <v>16.96394485435333</v>
+        <v>0.2012356565663357</v>
       </c>
       <c r="N23" t="n">
-        <v>20.1074768223395</v>
+        <v>0.2415841359378594</v>
       </c>
       <c r="O23" t="n">
-        <v>13.53137395626745</v>
+        <v>0.1604754449162009</v>
       </c>
       <c r="P23" t="n">
-        <v>16.38505669031947</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>11.5269689561966</v>
-      </c>
+        <v>0.1707961234614934</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>15.78349285886084</v>
+        <v>22.53920047150602</v>
       </c>
       <c r="S23" t="n">
-        <v>10.35243538966747</v>
+        <v>22.81954030511663</v>
       </c>
       <c r="T23" t="n">
-        <v>12.06019982887776</v>
+        <v>19.00368568130099</v>
       </c>
       <c r="U23" t="n">
-        <v>8.97035348508121</v>
+        <v>21.09606226663865</v>
       </c>
       <c r="V23" t="n">
-        <v>11.47178478380785</v>
+        <v>16.96363921823133</v>
       </c>
       <c r="W23" t="n">
-        <v>9.459498933516496</v>
+        <v>20.10691486188664</v>
       </c>
       <c r="X23" t="n">
-        <v>11.43223308880649</v>
+        <v>13.53016376763221</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.808030361489015</v>
+        <v>16.38455421554414</v>
       </c>
       <c r="Z23" t="n">
-        <v>9.905169257258011</v>
+        <v>11.52764343471356</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.3263787111344236</v>
+        <v>15.78418071327979</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.181662752733211</v>
+        <v>10.35329614435092</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1284338843604091</v>
+        <v>12.05963139874864</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.1056534255332669</v>
+        <v>8.970569423925873</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.08000121353462955</v>
+        <v>11.47144991524152</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.06598147671331374</v>
+        <v>9.459906586831552</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.05353943267067715</v>
+        <v>11.43124002114611</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.0608235770696868</v>
+        <v>8.808588198606607</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.0461861648779579</v>
+        <v>9.904932038343855</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22.74665012931053</v>
+        <v>0.3265976923243319</v>
       </c>
       <c r="AK23" t="n">
-        <v>18.92226511174243</v>
+        <v>0.1817538821709471</v>
       </c>
       <c r="AL23" t="n">
-        <v>17.76286379447079</v>
+        <v>0.1279761490936577</v>
       </c>
       <c r="AM23" t="n">
+        <v>0.105506298140767</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.08014953130506162</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.06585470450365075</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.05297467120684831</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.06099827435005199</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.0467101927341684</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>22.74556877607963</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>18.92269271897744</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>17.76296309444843</v>
+      </c>
+      <c r="AV23" t="n">
         <v>15.27650844477093</v>
       </c>
-      <c r="AN23" t="n">
-        <v>13.65180949892831</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>12.57549007358213</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>11.52495477410781</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>11.4357626753187</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>10.57689045874617</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>12.67678379959479</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>10.0570628676878</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>9.190134877393316</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.068422178154483</v>
-      </c>
       <c r="AW23" t="n">
-        <v>9.853519236791698</v>
+        <v>13.65297962466725</v>
       </c>
       <c r="AX23" t="n">
-        <v>10.19394807025654</v>
+        <v>12.57520220618005</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.1926895308419</v>
+        <v>11.52402017755225</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9.897505399610777</v>
+        <v>11.4353276596786</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.501454920113849</v>
+        <v>10.57796810406074</v>
       </c>
       <c r="BB23" t="n">
+        <v>12.67633031532225</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>10.0568967694602</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>9.190878358459544</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.068561308748281</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>9.853354371401704</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>10.19407282637679</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>10.19261079100159</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>9.897066231969957</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9.501722336946131</v>
+      </c>
+      <c r="BK23" t="n">
         <v>45.87313742095809</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>35.85684255333614</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>29.23516267856407</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>22.98649489087932</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>22.93073093149522</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>22.10566728953889</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>21.82803605216779</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>21.82803605216779</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>21.82803605216779</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>47.4078330192274</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>39.19623370736154</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>38.68424812028248</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>38.05798899463541</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>37.36487937256476</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>37.31388904670047</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>36.93561253971851</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>35.21882720184879</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>35.08017133727587</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2920205224227208</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2166967678117371</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2448254357586426</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.1466026441264714</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.1660398637419016</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.2686126495093393</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.2429775524418554</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.06603843549066137</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.23168181838897</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>8.808588198606607</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>9.904932038343855</v>
       </c>
     </row>
   </sheetData>
